--- a/Data Files/File_S12.xlsx
+++ b/Data Files/File_S12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Michael/Downloads/2025_supplement_stripped_names/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhangxiang/Documents/Research_CB/GIN/manuscript/GIN/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81DA5FA-7A37-E245-8669-01E71B5E6531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC73D936-BDA7-274C-B011-F19550CF7DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38140" windowHeight="15940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38140" windowHeight="15940" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="3" r:id="rId1"/>
@@ -49,12 +49,6 @@
     <t>L1_cluster_genes</t>
   </si>
   <si>
-    <t>L0_cluster_ID</t>
-  </si>
-  <si>
-    <t>L0_cluster_genes</t>
-  </si>
-  <si>
     <t>C11orf48</t>
   </si>
   <si>
@@ -1078,7 +1072,13 @@
     <t>Compute sum of GO terms + citations and select genes with a sum &lt;=15.</t>
   </si>
   <si>
-    <t>113 poorly characterized genes  that map to the HAP1 genetic interaction profile similarity network</t>
+    <t>113 poorly characterized genes that map to the HAP1 genetic interaction profile similarity network</t>
+  </si>
+  <si>
+    <t>L2_cluster_ID</t>
+  </si>
+  <si>
+    <t>L2_cluster_genes</t>
   </si>
 </sst>
 </file>
@@ -1344,17 +1344,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
@@ -1397,24 +1397,24 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1429,21 +1429,21 @@
         <v>1375</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>3625</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1458,21 +1458,21 @@
         <v>1102</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>2633</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1487,21 +1487,21 @@
         <v>286</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H4">
         <v>2191</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1516,21 +1516,21 @@
         <v>1005</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H5">
         <v>156</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1545,21 +1545,21 @@
         <v>1212</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6">
         <v>1363</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1574,21 +1574,21 @@
         <v>933</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H7">
         <v>1825</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1603,21 +1603,21 @@
         <v>207</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H8">
         <v>107</v>
       </c>
       <c r="I8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1632,21 +1632,21 @@
         <v>246</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9">
         <v>2500</v>
       </c>
       <c r="I9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1661,21 +1661,21 @@
         <v>562</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H10">
         <v>1926</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1690,21 +1690,21 @@
         <v>1130</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H11">
         <v>1548</v>
       </c>
       <c r="I11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1719,21 +1719,21 @@
         <v>410</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H12">
         <v>927</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1748,21 +1748,21 @@
         <v>448</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>2356</v>
       </c>
       <c r="I13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1777,21 +1777,21 @@
         <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H14">
         <v>1952</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1806,21 +1806,21 @@
         <v>374</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H15">
         <v>4784</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1835,21 +1835,21 @@
         <v>519</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H16">
         <v>1810</v>
       </c>
       <c r="I16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1864,21 +1864,21 @@
         <v>1034</v>
       </c>
       <c r="G17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H17">
         <v>647</v>
       </c>
       <c r="I17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1893,21 +1893,21 @@
         <v>362</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H18">
         <v>523</v>
       </c>
       <c r="I18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1922,21 +1922,21 @@
         <v>1238</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H19">
         <v>270</v>
       </c>
       <c r="I19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1951,21 +1951,21 @@
         <v>1110</v>
       </c>
       <c r="G20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H20">
         <v>4016</v>
       </c>
       <c r="I20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -1980,21 +1980,21 @@
         <v>1293</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H21">
         <v>2539</v>
       </c>
       <c r="I21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2009,21 +2009,21 @@
         <v>539</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H22">
         <v>3917</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -2038,21 +2038,21 @@
         <v>368</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H23">
         <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2067,21 +2067,21 @@
         <v>1393</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H24">
         <v>2394</v>
       </c>
       <c r="I24" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -2096,21 +2096,21 @@
         <v>401</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H25">
         <v>2679</v>
       </c>
       <c r="I25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>4</v>
@@ -2125,21 +2125,21 @@
         <v>709</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H26">
         <v>1355</v>
       </c>
       <c r="I26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C27">
         <v>4</v>
@@ -2154,21 +2154,21 @@
         <v>1024</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H27">
         <v>3443</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -2183,21 +2183,21 @@
         <v>257</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H28">
         <v>2460</v>
       </c>
       <c r="I28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>4</v>
@@ -2212,21 +2212,21 @@
         <v>81</v>
       </c>
       <c r="G29" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H29">
         <v>448</v>
       </c>
       <c r="I29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>4</v>
@@ -2241,21 +2241,21 @@
         <v>22</v>
       </c>
       <c r="G30" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H30">
         <v>53</v>
       </c>
       <c r="I30" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -2270,21 +2270,21 @@
         <v>1218</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H31">
         <v>4234</v>
       </c>
       <c r="I31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -2299,21 +2299,21 @@
         <v>240</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H32">
         <v>2691</v>
       </c>
       <c r="I32" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -2328,21 +2328,21 @@
         <v>1066</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H33">
         <v>2767</v>
       </c>
       <c r="I33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -2357,21 +2357,21 @@
         <v>554</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H34">
         <v>2184</v>
       </c>
       <c r="I34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -2386,21 +2386,21 @@
         <v>906</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H35">
         <v>161</v>
       </c>
       <c r="I35" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>6</v>
@@ -2415,21 +2415,21 @@
         <v>271</v>
       </c>
       <c r="G36" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H36">
         <v>4179</v>
       </c>
       <c r="I36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B37" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -2444,21 +2444,21 @@
         <v>954</v>
       </c>
       <c r="G37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H37">
         <v>3077</v>
       </c>
       <c r="I37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C38">
         <v>6</v>
@@ -2473,21 +2473,21 @@
         <v>481</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H38">
         <v>3403</v>
       </c>
       <c r="I38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -2502,21 +2502,21 @@
         <v>1105</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H39">
         <v>4103</v>
       </c>
       <c r="I39" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -2531,21 +2531,21 @@
         <v>647</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H40">
         <v>728</v>
       </c>
       <c r="I40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C41">
         <v>7</v>
@@ -2560,21 +2560,21 @@
         <v>425</v>
       </c>
       <c r="G41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H41">
         <v>3683</v>
       </c>
       <c r="I41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B42" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C42">
         <v>7</v>
@@ -2589,21 +2589,21 @@
         <v>1204</v>
       </c>
       <c r="G42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H42">
         <v>2740</v>
       </c>
       <c r="I42" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -2618,21 +2618,21 @@
         <v>618</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H43">
         <v>846</v>
       </c>
       <c r="I43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C44">
         <v>7</v>
@@ -2647,21 +2647,21 @@
         <v>1393</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H44">
         <v>2394</v>
       </c>
       <c r="I44" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C45">
         <v>7</v>
@@ -2676,21 +2676,21 @@
         <v>6</v>
       </c>
       <c r="G45" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H45">
         <v>539</v>
       </c>
       <c r="I45" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C46">
         <v>7</v>
@@ -2705,21 +2705,21 @@
         <v>368</v>
       </c>
       <c r="G46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H46">
         <v>112</v>
       </c>
       <c r="I46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C47">
         <v>7</v>
@@ -2734,21 +2734,21 @@
         <v>1183</v>
       </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H47">
         <v>1874</v>
       </c>
       <c r="I47" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B48" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C48">
         <v>8</v>
@@ -2763,21 +2763,21 @@
         <v>922</v>
       </c>
       <c r="G48" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H48">
         <v>460</v>
       </c>
       <c r="I48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>8</v>
@@ -2792,21 +2792,21 @@
         <v>1265</v>
       </c>
       <c r="G49" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H49">
         <v>2462</v>
       </c>
       <c r="I49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B50" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C50">
         <v>8</v>
@@ -2821,21 +2821,21 @@
         <v>67</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H50">
         <v>1969</v>
       </c>
       <c r="I50" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C51">
         <v>8</v>
@@ -2850,21 +2850,21 @@
         <v>610</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H51">
         <v>3662</v>
       </c>
       <c r="I51" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B52" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C52">
         <v>8</v>
@@ -2879,21 +2879,21 @@
         <v>398</v>
       </c>
       <c r="G52" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H52">
         <v>3959</v>
       </c>
       <c r="I52" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C53">
         <v>8</v>
@@ -2908,21 +2908,21 @@
         <v>339</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H53">
         <v>249</v>
       </c>
       <c r="I53" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C54">
         <v>8</v>
@@ -2937,21 +2937,21 @@
         <v>189</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H54">
         <v>326</v>
       </c>
       <c r="I54" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C55">
         <v>9</v>
@@ -2966,21 +2966,21 @@
         <v>272</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H55">
         <v>983</v>
       </c>
       <c r="I55" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C56">
         <v>9</v>
@@ -2995,21 +2995,21 @@
         <v>149</v>
       </c>
       <c r="G56" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H56">
         <v>138</v>
       </c>
       <c r="I56" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C57">
         <v>9</v>
@@ -3024,21 +3024,21 @@
         <v>775</v>
       </c>
       <c r="G57" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H57">
         <v>565</v>
       </c>
       <c r="I57" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C58">
         <v>9</v>
@@ -3053,21 +3053,21 @@
         <v>700</v>
       </c>
       <c r="G58" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H58">
         <v>2188</v>
       </c>
       <c r="I58" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C59">
         <v>8</v>
@@ -3082,21 +3082,21 @@
         <v>1317</v>
       </c>
       <c r="G59" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H59">
         <v>1569</v>
       </c>
       <c r="I59" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B60" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C60">
         <v>9</v>
@@ -3111,21 +3111,21 @@
         <v>967</v>
       </c>
       <c r="G60" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H60">
         <v>3527</v>
       </c>
       <c r="I60" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C61">
         <v>9</v>
@@ -3140,21 +3140,21 @@
         <v>869</v>
       </c>
       <c r="G61" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H61">
         <v>1480</v>
       </c>
       <c r="I61" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C62">
         <v>9</v>
@@ -3169,21 +3169,21 @@
         <v>269</v>
       </c>
       <c r="G62" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H62">
         <v>2103</v>
       </c>
       <c r="I62" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C63">
         <v>9</v>
@@ -3198,21 +3198,21 @@
         <v>362</v>
       </c>
       <c r="G63" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H63">
         <v>536</v>
       </c>
       <c r="I63" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C64">
         <v>9</v>
@@ -3227,21 +3227,21 @@
         <v>58</v>
       </c>
       <c r="G64" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H64">
         <v>3049</v>
       </c>
       <c r="I64" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C65">
         <v>7</v>
@@ -3256,21 +3256,21 @@
         <v>1253</v>
       </c>
       <c r="G65" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H65">
         <v>1809</v>
       </c>
       <c r="I65" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C66">
         <v>10</v>
@@ -3285,21 +3285,21 @@
         <v>1257</v>
       </c>
       <c r="G66" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H66">
         <v>833</v>
       </c>
       <c r="I66" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C67">
         <v>10</v>
@@ -3314,21 +3314,21 @@
         <v>1109</v>
       </c>
       <c r="G67" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H67">
         <v>3134</v>
       </c>
       <c r="I67" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C68">
         <v>10</v>
@@ -3343,21 +3343,21 @@
         <v>640</v>
       </c>
       <c r="G68" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H68">
         <v>1827</v>
       </c>
       <c r="I68" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B69" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C69">
         <v>10</v>
@@ -3372,21 +3372,21 @@
         <v>890</v>
       </c>
       <c r="G69" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H69">
         <v>1488</v>
       </c>
       <c r="I69" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B70" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C70">
         <v>10</v>
@@ -3401,21 +3401,21 @@
         <v>1375</v>
       </c>
       <c r="G70" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H70">
         <v>1925</v>
       </c>
       <c r="I70" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C71">
         <v>9</v>
@@ -3430,21 +3430,21 @@
         <v>661</v>
       </c>
       <c r="G71" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H71">
         <v>3437</v>
       </c>
       <c r="I71" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C72">
         <v>10</v>
@@ -3459,21 +3459,21 @@
         <v>1217</v>
       </c>
       <c r="G72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H72">
         <v>2963</v>
       </c>
       <c r="I72" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C73">
         <v>10</v>
@@ -3488,21 +3488,21 @@
         <v>779</v>
       </c>
       <c r="G73" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H73">
         <v>1621</v>
       </c>
       <c r="I73" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B74" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C74">
         <v>10</v>
@@ -3517,21 +3517,21 @@
         <v>1102</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H74">
         <v>2633</v>
       </c>
       <c r="I74" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C75">
         <v>11</v>
@@ -3546,21 +3546,21 @@
         <v>296</v>
       </c>
       <c r="G75" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H75">
         <v>3385</v>
       </c>
       <c r="I75" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C76">
         <v>11</v>
@@ -3575,21 +3575,21 @@
         <v>524</v>
       </c>
       <c r="G76" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H76">
         <v>811</v>
       </c>
       <c r="I76" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C77">
         <v>10</v>
@@ -3604,21 +3604,21 @@
         <v>1186</v>
       </c>
       <c r="G77" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H77">
         <v>276</v>
       </c>
       <c r="I77" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B78" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C78">
         <v>11</v>
@@ -3633,21 +3633,21 @@
         <v>610</v>
       </c>
       <c r="G78" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H78">
         <v>3662</v>
       </c>
       <c r="I78" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C79">
         <v>11</v>
@@ -3662,21 +3662,21 @@
         <v>609</v>
       </c>
       <c r="G79" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H79">
         <v>2277</v>
       </c>
       <c r="I79" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C80">
         <v>11</v>
@@ -3691,21 +3691,21 @@
         <v>720</v>
       </c>
       <c r="G80" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H80">
         <v>4034</v>
       </c>
       <c r="I80" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C81">
         <v>11</v>
@@ -3720,21 +3720,21 @@
         <v>1205</v>
       </c>
       <c r="G81" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H81">
         <v>3421</v>
       </c>
       <c r="I81" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C82">
         <v>11</v>
@@ -3749,21 +3749,21 @@
         <v>81</v>
       </c>
       <c r="G82" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H82">
         <v>448</v>
       </c>
       <c r="I82" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C83">
         <v>11</v>
@@ -3778,21 +3778,21 @@
         <v>68</v>
       </c>
       <c r="G83" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H83">
         <v>4008</v>
       </c>
       <c r="I83" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B84" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C84">
         <v>10</v>
@@ -3807,21 +3807,21 @@
         <v>154</v>
       </c>
       <c r="G84" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H84">
         <v>1757</v>
       </c>
       <c r="I84" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C85">
         <v>12</v>
@@ -3836,21 +3836,21 @@
         <v>1061</v>
       </c>
       <c r="G85" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H85">
         <v>4044</v>
       </c>
       <c r="I85" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B86" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C86">
         <v>12</v>
@@ -3865,21 +3865,21 @@
         <v>81</v>
       </c>
       <c r="G86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H86">
         <v>376</v>
       </c>
       <c r="I86" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C87">
         <v>12</v>
@@ -3894,21 +3894,21 @@
         <v>90</v>
       </c>
       <c r="G87" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H87">
         <v>2378</v>
       </c>
       <c r="I87" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B88" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C88">
         <v>12</v>
@@ -3923,21 +3923,21 @@
         <v>1101</v>
       </c>
       <c r="G88" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H88">
         <v>252</v>
       </c>
       <c r="I88" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B89" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C89">
         <v>13</v>
@@ -3952,21 +3952,21 @@
         <v>1137</v>
       </c>
       <c r="G89" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H89">
         <v>3264</v>
       </c>
       <c r="I89" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B90" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C90">
         <v>13</v>
@@ -3981,21 +3981,21 @@
         <v>663</v>
       </c>
       <c r="G90" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H90">
         <v>1443</v>
       </c>
       <c r="I90" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B91" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C91">
         <v>13</v>
@@ -4010,21 +4010,21 @@
         <v>776</v>
       </c>
       <c r="G91" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H91">
         <v>605</v>
       </c>
       <c r="I91" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C92">
         <v>13</v>
@@ -4039,21 +4039,21 @@
         <v>128</v>
       </c>
       <c r="G92" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H92">
         <v>1250</v>
       </c>
       <c r="I92" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C93">
         <v>13</v>
@@ -4068,21 +4068,21 @@
         <v>262</v>
       </c>
       <c r="G93" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H93">
         <v>3272</v>
       </c>
       <c r="I93" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C94">
         <v>13</v>
@@ -4097,21 +4097,21 @@
         <v>6</v>
       </c>
       <c r="G94" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H94">
         <v>526</v>
       </c>
       <c r="I94" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C95">
         <v>13</v>
@@ -4126,21 +4126,21 @@
         <v>1356</v>
       </c>
       <c r="G95" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H95">
         <v>4595</v>
       </c>
       <c r="I95" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B96" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C96">
         <v>11</v>
@@ -4155,21 +4155,21 @@
         <v>860</v>
       </c>
       <c r="G96" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H96">
         <v>1113</v>
       </c>
       <c r="I96" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B97" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C97">
         <v>13</v>
@@ -4184,21 +4184,21 @@
         <v>804</v>
       </c>
       <c r="G97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H97">
         <v>2313</v>
       </c>
       <c r="I97" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B98" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C98">
         <v>14</v>
@@ -4213,21 +4213,21 @@
         <v>816</v>
       </c>
       <c r="G98" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H98">
         <v>3121</v>
       </c>
       <c r="I98" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C99">
         <v>14</v>
@@ -4242,21 +4242,21 @@
         <v>999</v>
       </c>
       <c r="G99" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H99">
         <v>1495</v>
       </c>
       <c r="I99" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B100" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C100">
         <v>13</v>
@@ -4271,21 +4271,21 @@
         <v>1138</v>
       </c>
       <c r="G100" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H100">
         <v>2529</v>
       </c>
       <c r="I100" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C101">
         <v>14</v>
@@ -4300,21 +4300,21 @@
         <v>169</v>
       </c>
       <c r="G101" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H101">
         <v>358</v>
       </c>
       <c r="I101" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C102">
         <v>14</v>
@@ -4329,21 +4329,21 @@
         <v>552</v>
       </c>
       <c r="G102" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H102">
         <v>2007</v>
       </c>
       <c r="I102" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B103" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C103">
         <v>10</v>
@@ -4358,21 +4358,21 @@
         <v>812</v>
       </c>
       <c r="G103" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H103">
         <v>3289</v>
       </c>
       <c r="I103" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C104">
         <v>11</v>
@@ -4387,21 +4387,21 @@
         <v>804</v>
       </c>
       <c r="G104" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H104">
         <v>4243</v>
       </c>
       <c r="I104" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C105">
         <v>9</v>
@@ -4416,21 +4416,21 @@
         <v>1250</v>
       </c>
       <c r="G105" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H105">
         <v>2635</v>
       </c>
       <c r="I105" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C106">
         <v>15</v>
@@ -4445,21 +4445,21 @@
         <v>41</v>
       </c>
       <c r="G106" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H106">
         <v>316</v>
       </c>
       <c r="I106" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C107">
         <v>15</v>
@@ -4474,21 +4474,21 @@
         <v>836</v>
       </c>
       <c r="G107" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H107">
         <v>2731</v>
       </c>
       <c r="I107" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B108" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C108">
         <v>15</v>
@@ -4503,21 +4503,21 @@
         <v>760</v>
       </c>
       <c r="G108" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="H108">
         <v>2606</v>
       </c>
       <c r="I108" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C109">
         <v>15</v>
@@ -4532,21 +4532,21 @@
         <v>197</v>
       </c>
       <c r="G109" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H109">
         <v>232</v>
       </c>
       <c r="I109" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B110" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C110">
         <v>15</v>
@@ -4561,21 +4561,21 @@
         <v>6</v>
       </c>
       <c r="G110" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H110">
         <v>539</v>
       </c>
       <c r="I110" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C111">
         <v>14</v>
@@ -4590,21 +4590,21 @@
         <v>326</v>
       </c>
       <c r="G111" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H111">
         <v>1996</v>
       </c>
       <c r="I111" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B112" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C112">
         <v>15</v>
@@ -4619,21 +4619,21 @@
         <v>1119</v>
       </c>
       <c r="G112" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H112">
         <v>2789</v>
       </c>
       <c r="I112" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C113">
         <v>15</v>
@@ -4648,21 +4648,21 @@
         <v>1129</v>
       </c>
       <c r="G113" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H113">
         <v>1879</v>
       </c>
       <c r="I113" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B114" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C114">
         <v>6</v>
@@ -4677,13 +4677,13 @@
         <v>115</v>
       </c>
       <c r="G114" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H114">
         <v>1349</v>
       </c>
       <c r="I114" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
